--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,506 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123801428</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567698</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6509701</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123807990</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567667</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6509653</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123807970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567653</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6509656</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123802060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567712</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6509726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>123801428</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123807990</v>
+        <v>123807970</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567667</v>
+        <v>567653</v>
       </c>
       <c r="R4" t="n">
-        <v>6509653</v>
+        <v>6509656</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807970</v>
+        <v>123807990</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567653</v>
+        <v>567667</v>
       </c>
       <c r="R5" t="n">
-        <v>6509656</v>
+        <v>6509653</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1155,7 +1155,7 @@
         <v>123802060</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301735</v>
       </c>
       <c r="B2" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801428</v>
+        <v>123807970</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567698</v>
+        <v>567653</v>
       </c>
       <c r="R3" t="n">
-        <v>6509701</v>
+        <v>6509656</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123807970</v>
+        <v>123802060</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567653</v>
+        <v>567712</v>
       </c>
       <c r="R4" t="n">
-        <v>6509656</v>
+        <v>6509726</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807990</v>
+        <v>123801428</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567667</v>
+        <v>567698</v>
       </c>
       <c r="R5" t="n">
-        <v>6509653</v>
+        <v>6509701</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802060</v>
+        <v>123807990</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567712</v>
+        <v>567667</v>
       </c>
       <c r="R6" t="n">
-        <v>6509726</v>
+        <v>6509653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123807970</v>
+        <v>123802060</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567653</v>
+        <v>567712</v>
       </c>
       <c r="R3" t="n">
-        <v>6509656</v>
+        <v>6509726</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802060</v>
+        <v>123807970</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567712</v>
+        <v>567653</v>
       </c>
       <c r="R4" t="n">
-        <v>6509726</v>
+        <v>6509656</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123801428</v>
+        <v>123807990</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567698</v>
+        <v>567667</v>
       </c>
       <c r="R5" t="n">
-        <v>6509701</v>
+        <v>6509653</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123807990</v>
+        <v>123801428</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567667</v>
+        <v>567698</v>
       </c>
       <c r="R6" t="n">
-        <v>6509653</v>
+        <v>6509701</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123807970</v>
+        <v>123801428</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567653</v>
+        <v>567698</v>
       </c>
       <c r="R4" t="n">
-        <v>6509656</v>
+        <v>6509701</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801428</v>
+        <v>123807970</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567698</v>
+        <v>567653</v>
       </c>
       <c r="R6" t="n">
-        <v>6509701</v>
+        <v>6509656</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802060</v>
+        <v>123801428</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567712</v>
+        <v>567698</v>
       </c>
       <c r="R3" t="n">
-        <v>6509726</v>
+        <v>6509701</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801428</v>
+        <v>123807970</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567698</v>
+        <v>567653</v>
       </c>
       <c r="R4" t="n">
-        <v>6509701</v>
+        <v>6509656</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807990</v>
+        <v>123802060</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567667</v>
+        <v>567712</v>
       </c>
       <c r="R5" t="n">
-        <v>6509653</v>
+        <v>6509726</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123807970</v>
+        <v>123807990</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567653</v>
+        <v>567667</v>
       </c>
       <c r="R6" t="n">
-        <v>6509656</v>
+        <v>6509653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801428</v>
+        <v>123802060</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567698</v>
+        <v>567712</v>
       </c>
       <c r="R3" t="n">
-        <v>6509701</v>
+        <v>6509726</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123807970</v>
+        <v>123807990</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567653</v>
+        <v>567667</v>
       </c>
       <c r="R4" t="n">
-        <v>6509656</v>
+        <v>6509653</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802060</v>
+        <v>123801428</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567712</v>
+        <v>567698</v>
       </c>
       <c r="R5" t="n">
-        <v>6509726</v>
+        <v>6509701</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123807990</v>
+        <v>123807970</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567667</v>
+        <v>567653</v>
       </c>
       <c r="R6" t="n">
-        <v>6509653</v>
+        <v>6509656</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123807970</v>
+        <v>123807990</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567653</v>
+        <v>567667</v>
       </c>
       <c r="R3" t="n">
-        <v>6509656</v>
+        <v>6509653</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801428</v>
+        <v>123802060</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567698</v>
+        <v>567712</v>
       </c>
       <c r="R4" t="n">
-        <v>6509701</v>
+        <v>6509726</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807990</v>
+        <v>123807970</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567667</v>
+        <v>567653</v>
       </c>
       <c r="R5" t="n">
-        <v>6509653</v>
+        <v>6509656</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802060</v>
+        <v>123801428</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567712</v>
+        <v>567698</v>
       </c>
       <c r="R6" t="n">
-        <v>6509726</v>
+        <v>6509701</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123807990</v>
+        <v>123801428</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567667</v>
+        <v>567698</v>
       </c>
       <c r="R3" t="n">
-        <v>6509653</v>
+        <v>6509701</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802060</v>
+        <v>123807970</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567712</v>
+        <v>567653</v>
       </c>
       <c r="R4" t="n">
-        <v>6509726</v>
+        <v>6509656</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807970</v>
+        <v>123807990</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567653</v>
+        <v>567667</v>
       </c>
       <c r="R5" t="n">
-        <v>6509656</v>
+        <v>6509653</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801428</v>
+        <v>123802060</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567698</v>
+        <v>567712</v>
       </c>
       <c r="R6" t="n">
-        <v>6509701</v>
+        <v>6509726</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,6 +1275,136 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125244703</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56492</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6509610</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>125244703</v>
       </c>
       <c r="B7" t="n">
-        <v>56492</v>
+        <v>56606</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1280,12 +1280,7 @@
         <v>125244703</v>
       </c>
       <c r="B7" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,6 +1400,129 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126258378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57454</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567667</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6509653</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1405,7 +1405,7 @@
         <v>126258378</v>
       </c>
       <c r="B8" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1405,7 +1405,7 @@
         <v>126258378</v>
       </c>
       <c r="B8" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1523,325 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129272748</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567658</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6509726</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129273218</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567653</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6509656</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129273185</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567664</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6509693</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>129272748</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129273218</v>
       </c>
       <c r="B10" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129273185</v>
       </c>
       <c r="B11" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1842,6 +1842,117 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129832493</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6509605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,6 +1953,236 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129866787</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567660</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6509653</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>E-Nor-0904</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129866788</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567705</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6509711</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>E-Nor-0903</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>129832493</v>
       </c>
       <c r="B12" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129866787</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129866788</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,121 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131468541</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58046</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567626</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6509625</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2188,7 +2188,7 @@
         <v>131289440</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>131289461</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -2398,7 +2398,7 @@
         <v>131468541</v>
       </c>
       <c r="B17" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123301735</v>
+        <v>129134693</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567659</v>
+        <v>567631</v>
       </c>
       <c r="R2" t="n">
-        <v>6509739</v>
+        <v>6509580</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +746,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hattdiameter 10 resp 12 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,83 +770,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801428</v>
+        <v>123301735</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567698</v>
+        <v>567659</v>
       </c>
       <c r="R3" t="n">
-        <v>6509701</v>
+        <v>6509739</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,70 +868,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123807970</v>
+        <v>129272748</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567653</v>
+        <v>567658</v>
       </c>
       <c r="R4" t="n">
-        <v>6509656</v>
+        <v>6509726</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,51 +995,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123807990</v>
+        <v>129832493</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567667</v>
+        <v>567675</v>
       </c>
       <c r="R5" t="n">
-        <v>6509653</v>
+        <v>6509605</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1063,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,51 +1106,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802060</v>
+        <v>129273185</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567712</v>
+        <v>567664</v>
       </c>
       <c r="R6" t="n">
-        <v>6509726</v>
+        <v>6509693</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,62 +1211,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125244703</v>
+        <v>129273218</v>
       </c>
       <c r="B7" t="n">
-        <v>56607</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208260</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Luvebo 2:1, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>567653</v>
       </c>
       <c r="R7" t="n">
-        <v>6509610</v>
+        <v>6509656</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,22 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126258378</v>
+        <v>131289440</v>
       </c>
       <c r="B8" t="n">
-        <v>57459</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,37 +1327,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1453,13 +1359,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567667</v>
+        <v>567626</v>
       </c>
       <c r="R8" t="n">
-        <v>6509653</v>
+        <v>6509625</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,22 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129272748</v>
+        <v>131289461</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,34 +1432,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567658</v>
+        <v>567680</v>
       </c>
       <c r="R9" t="n">
-        <v>6509726</v>
+        <v>6509667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,12 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,7 +1508,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1634,55 +1526,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129273218</v>
+        <v>128982344</v>
       </c>
       <c r="B10" t="n">
-        <v>92908</v>
+        <v>56895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567653</v>
+        <v>567631</v>
       </c>
       <c r="R10" t="n">
-        <v>6509656</v>
+        <v>6509580</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,17 +1603,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,52 +1651,66 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129273185</v>
+        <v>126725365</v>
       </c>
       <c r="B11" t="n">
-        <v>92908</v>
+        <v>45044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567664</v>
+        <v>567631</v>
       </c>
       <c r="R11" t="n">
-        <v>6509693</v>
+        <v>6509580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,17 +1732,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,48 +1780,66 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129832493</v>
+        <v>126633775</v>
       </c>
       <c r="B12" t="n">
-        <v>91662</v>
+        <v>45049</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>102021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567675</v>
+        <v>567631</v>
       </c>
       <c r="R12" t="n">
-        <v>6509605</v>
+        <v>6509580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,27 +1861,32 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Summerat för alla observationspunkterna vid Sjöberga. Men de flesta vid Göstas äng.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,51 +1914,58 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129866787</v>
+        <v>126258378</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>57754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luvebo 2:1, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567660</v>
+        <v>567667</v>
       </c>
       <c r="R13" t="n">
         <v>6509653</v>
@@ -2027,19 +1993,24 @@
           <t>Simonstorp</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>E-Nor-0904</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,7 +2025,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2062,65 +2033,60 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129866788</v>
+        <v>131468541</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Luvebo 2:1, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567705</v>
+        <v>567626</v>
       </c>
       <c r="R14" t="n">
-        <v>6509711</v>
+        <v>6509625</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2142,19 +2108,24 @@
           <t>Simonstorp</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>E-Nor-0903</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,7 +2140,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2177,61 +2148,70 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131289440</v>
+        <v>126725469</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>43378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>201075</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567626</v>
+        <v>567631</v>
       </c>
       <c r="R15" t="n">
-        <v>6509625</v>
+        <v>6509580</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,17 +2233,27 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,6 +2262,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131289461</v>
+        <v>126725343</v>
       </c>
       <c r="B16" t="n">
-        <v>57901</v>
+        <v>43258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,16 +2292,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>201129</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2318,25 +2309,38 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567680</v>
+        <v>567631</v>
       </c>
       <c r="R16" t="n">
-        <v>6509667</v>
+        <v>6509580</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,17 +2362,27 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,6 +2391,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2395,53 +2410,66 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131468541</v>
+        <v>126674336</v>
       </c>
       <c r="B17" t="n">
-        <v>58073</v>
+        <v>43309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>201146</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Luvebo 2:1, Ög</t>
+          <t>Sjöberga, Göstas äng, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567626</v>
+        <v>567631</v>
       </c>
       <c r="R17" t="n">
-        <v>6509625</v>
+        <v>6509580</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,27 +2491,27 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Simonstorp</t>
+          <t>Kvillinge</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,6 +2520,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2507,6 +2536,1089 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126633596</v>
+      </c>
+      <c r="B18" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjöberga, Göstas äng, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567631</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6509580</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125244703</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567653</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6509610</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123801428</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567698</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6509701</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123802060</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567712</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6509726</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123807970</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567653</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6509656</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123807990</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567667</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6509653</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129866787</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567660</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6509653</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>E-Nor-0904</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129866788</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Luvebo 2:1, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567705</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6509711</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>E-Nor-0903</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129866829</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567588</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6509596</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3616,6 +3616,108 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135331701</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107696</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sjöberga, Göstas äng, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567631</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6509580</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301735</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129272748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129832493</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273185</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131289440</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131289461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982344</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126725365</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126633775</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2030,6 +2090,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131468541</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2274,6 +2344,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126725469</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2403,6 +2478,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126725343</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2532,6 +2612,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674336</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2665,6 +2750,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126633596</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2790,6 +2880,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125244703</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2910,6 +3005,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123801428</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3030,6 +3130,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3150,6 +3255,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123807970</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3270,6 +3380,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123807990</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3385,6 +3500,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866787</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3500,6 +3620,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866788</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3613,6 +3738,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866829</t>
         </is>
       </c>
     </row>
@@ -3717,8 +3847,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -1977,7 +1977,7 @@
         <v>126258378</v>
       </c>
       <c r="B13" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135331701</v>
       </c>
       <c r="B27" t="n">
-        <v>107696</v>
+        <v>107751</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -3751,7 +3751,7 @@
         <v>135331701</v>
       </c>
       <c r="B27" t="n">
-        <v>107751</v>
+        <v>107778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -3751,7 +3751,7 @@
         <v>135331701</v>
       </c>
       <c r="B27" t="n">
-        <v>107778</v>
+        <v>107783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11085-2025 artfynd.xlsx
+++ b/artfynd/A 11085-2025 artfynd.xlsx
@@ -3751,7 +3751,7 @@
         <v>135331701</v>
       </c>
       <c r="B27" t="n">
-        <v>107783</v>
+        <v>107785</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
